--- a/reports/2026-08_月次実績報告/excel/【営業会議資料】令和8年8月実績.xlsx
+++ b/reports/2026-08_月次実績報告/excel/【営業会議資料】令和8年8月実績.xlsx
@@ -9360,7 +9360,7 @@
       <c r="C88" s="51" t="n"/>
       <c r="D88" s="52" t="inlineStr">
         <is>
-          <t>馬場部長（東京）</t>
+          <t>馬場所長（東京）</t>
         </is>
       </c>
       <c r="E88" s="106" t="n"/>
@@ -9617,7 +9617,7 @@
       <c r="C91" s="51" t="n"/>
       <c r="D91" s="52" t="inlineStr">
         <is>
-          <t>高橋</t>
+          <t>馬場部長（東京）</t>
         </is>
       </c>
       <c r="E91" s="106" t="n"/>
@@ -9879,23 +9879,24 @@
       </c>
       <c r="E94" s="217" t="n"/>
       <c r="F94" s="319">
-        <f>F76+F85+F88</f>
+        <f>F76+F85+F88+F91</f>
         <v/>
       </c>
       <c r="G94" s="320">
-        <f>G76+G85+G88</f>
+        <f>G76+G85+G88+G91</f>
         <v/>
       </c>
       <c r="H94" s="320">
-        <f>H76+H85+H88</f>
+        <f>H76+H85+H88+H91</f>
         <v/>
       </c>
       <c r="I94" s="320">
-        <f>I76+I85+I88</f>
-        <v/>
-      </c>
-      <c r="J94" s="321" t="n">
-        <v>66</v>
+        <f>I76+I85+I88+I91</f>
+        <v/>
+      </c>
+      <c r="J94" s="321">
+        <f>I94-H94</f>
+        <v/>
       </c>
       <c r="K94" s="321">
         <f>I94-G94</f>
@@ -9906,19 +9907,19 @@
         <v/>
       </c>
       <c r="M94" s="319">
-        <f>M76+M85+M88</f>
+        <f>M76+M85+M88+M91</f>
         <v/>
       </c>
       <c r="N94" s="320">
-        <f>N76+N85+N88</f>
+        <f>N76+N85+N88+N91</f>
         <v/>
       </c>
       <c r="O94" s="320">
-        <f>O76+O85+O88</f>
+        <f>O76+O85+O88+O91</f>
         <v/>
       </c>
       <c r="P94" s="320">
-        <f>P76+P85+P88</f>
+        <f>P76+P85+P88+P91</f>
         <v/>
       </c>
       <c r="Q94" s="321">
@@ -10060,19 +10061,19 @@
         </is>
       </c>
       <c r="F96" s="275">
-        <f>F78+F87+F90</f>
+        <f>F78+F87+F90+F93</f>
         <v/>
       </c>
       <c r="G96" s="276">
-        <f>G78+G87+G90</f>
+        <f>G78+G87+G90+G93</f>
         <v/>
       </c>
       <c r="H96" s="276">
-        <f>H78+H87+H90</f>
+        <f>H78+H87+H90+H93</f>
         <v/>
       </c>
       <c r="I96" s="276">
-        <f>I78+I87+I90</f>
+        <f>I78+I87+I90+I93</f>
         <v/>
       </c>
       <c r="J96" s="278">
@@ -10088,19 +10089,19 @@
         <v/>
       </c>
       <c r="M96" s="226">
-        <f>M78+M87+M90</f>
+        <f>M78+M87+M90+M93</f>
         <v/>
       </c>
       <c r="N96" s="227">
-        <f>N78+N87+N90</f>
+        <f>N78+N87+N90+N93</f>
         <v/>
       </c>
       <c r="O96" s="276">
-        <f>O78+O87+O90</f>
+        <f>O78+O87+O90+O93</f>
         <v/>
       </c>
       <c r="P96" s="276">
-        <f>P78+P87+P90</f>
+        <f>P78+P87+P90+P93</f>
         <v/>
       </c>
       <c r="Q96" s="278">
@@ -21116,7 +21117,7 @@
       <c r="C88" s="51" t="n"/>
       <c r="D88" s="52" t="inlineStr">
         <is>
-          <t>馬場部長（東京）</t>
+          <t>馬場所長（東京）</t>
         </is>
       </c>
       <c r="E88" s="106" t="n"/>
@@ -21373,7 +21374,7 @@
       <c r="C91" s="51" t="n"/>
       <c r="D91" s="52" t="inlineStr">
         <is>
-          <t>高橋</t>
+          <t>馬場部長（東京）</t>
         </is>
       </c>
       <c r="E91" s="106" t="n"/>
@@ -21635,23 +21636,24 @@
       </c>
       <c r="E94" s="217" t="n"/>
       <c r="F94" s="319">
-        <f>F76+F85+F88</f>
+        <f>F76+F85+F88+F91</f>
         <v/>
       </c>
       <c r="G94" s="320">
-        <f>G76+G85+G88</f>
+        <f>G76+G85+G88+G91</f>
         <v/>
       </c>
       <c r="H94" s="320">
-        <f>H76+H85+H88</f>
+        <f>H76+H85+H88+H91</f>
         <v/>
       </c>
       <c r="I94" s="320">
-        <f>I76+I85+I88</f>
-        <v/>
-      </c>
-      <c r="J94" s="321" t="n">
-        <v>66</v>
+        <f>I76+I85+I88+I91</f>
+        <v/>
+      </c>
+      <c r="J94" s="321">
+        <f>I94-H94</f>
+        <v/>
       </c>
       <c r="K94" s="321">
         <f>I94-G94</f>
@@ -21662,19 +21664,19 @@
         <v/>
       </c>
       <c r="M94" s="319">
-        <f>M76+M85+M88</f>
+        <f>M76+M85+M88+M91</f>
         <v/>
       </c>
       <c r="N94" s="320">
-        <f>N76+N85+N88</f>
+        <f>N76+N85+N88+N91</f>
         <v/>
       </c>
       <c r="O94" s="320">
-        <f>O76+O85+O88</f>
+        <f>O76+O85+O88+O91</f>
         <v/>
       </c>
       <c r="P94" s="320">
-        <f>P76+P85+P88</f>
+        <f>P76+P85+P88+P91</f>
         <v/>
       </c>
       <c r="Q94" s="321">
@@ -21816,19 +21818,19 @@
         </is>
       </c>
       <c r="F96" s="275">
-        <f>F78+F87+F90</f>
+        <f>F78+F87+F90+F93</f>
         <v/>
       </c>
       <c r="G96" s="276">
-        <f>G78+G87+G90</f>
+        <f>G78+G87+G90+G93</f>
         <v/>
       </c>
       <c r="H96" s="276">
-        <f>H78+H87+H90</f>
+        <f>H78+H87+H90+H93</f>
         <v/>
       </c>
       <c r="I96" s="276">
-        <f>I78+I87+I90</f>
+        <f>I78+I87+I90+I93</f>
         <v/>
       </c>
       <c r="J96" s="278">
@@ -21844,19 +21846,19 @@
         <v/>
       </c>
       <c r="M96" s="275">
-        <f>M78+M87+M90</f>
+        <f>M78+M87+M90+M93</f>
         <v/>
       </c>
       <c r="N96" s="276">
-        <f>N78+N87+N90</f>
+        <f>N78+N87+N90+N93</f>
         <v/>
       </c>
       <c r="O96" s="276">
-        <f>O78+O87+O90</f>
+        <f>O78+O87+O90+O93</f>
         <v/>
       </c>
       <c r="P96" s="276">
-        <f>P78+P87+P90</f>
+        <f>P78+P87+P90+P93</f>
         <v/>
       </c>
       <c r="Q96" s="278">

--- a/reports/2026-08_月次実績報告/excel/【営業会議資料】令和8年8月実績.xlsx
+++ b/reports/2026-08_月次実績報告/excel/【営業会議資料】令和8年8月実績.xlsx
@@ -7088,7 +7088,7 @@
         <v>2280</v>
       </c>
       <c r="P59" s="285" t="n">
-        <v>2625.623</v>
+        <v>2620.623</v>
       </c>
       <c r="Q59" s="286">
         <f>P59-O59</f>
@@ -9655,7 +9655,7 @@
         <v>530</v>
       </c>
       <c r="P91" s="285" t="n">
-        <v>715.4935</v>
+        <v>712.8835</v>
       </c>
       <c r="Q91" s="286">
         <f>P91-O91</f>
@@ -18845,7 +18845,7 @@
         <v>11660</v>
       </c>
       <c r="P59" s="285" t="n">
-        <v>14709.1601</v>
+        <v>14704.1601</v>
       </c>
       <c r="Q59" s="286">
         <f>P59-O59</f>
@@ -21412,7 +21412,7 @@
         <v>3925</v>
       </c>
       <c r="P91" s="285" t="n">
-        <v>3184.4425</v>
+        <v>3181.8325</v>
       </c>
       <c r="Q91" s="286">
         <f>P91-O91</f>
